--- a/dataset/TSTR_ML_Results_All_Metrics.xlsx
+++ b/dataset/TSTR_ML_Results_All_Metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,32 +446,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>T3_Beta_Crop</t>
+          <t>T4_Beta_Final</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>T4_Beta_Final</t>
+          <t>T5_Copula</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>T5_Copula</t>
+          <t>T7_AHAPSF</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T6_Best_Copula</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>T7_AHAPSF</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>T8_Hybrid_Final</t>
+          <t>T9_LHS</t>
         </is>
       </c>
     </row>
@@ -488,22 +478,16 @@
         <v>0.9806</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9327</v>
+        <v>0.9347</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9347</v>
+        <v>0.9735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9735</v>
+        <v>0.9745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.9714</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="3">
@@ -519,22 +503,16 @@
         <v>0.9825</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9412</v>
+        <v>0.9434</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9434</v>
+        <v>0.9754</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9754</v>
+        <v>0.9748</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8809</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9748</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.9717</v>
+        <v>0.989</v>
       </c>
     </row>
     <row r="4">
@@ -550,22 +528,16 @@
         <v>0.9806</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9327</v>
+        <v>0.9347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9347</v>
+        <v>0.9735</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9735</v>
+        <v>0.9745</v>
       </c>
       <c r="G4" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.9714</v>
+        <v>0.9888</v>
       </c>
     </row>
     <row r="5">
@@ -581,22 +553,16 @@
         <v>0.9804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9341</v>
+        <v>0.9734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9734</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8824</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9743000000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.9712</v>
+        <v>0.9887</v>
       </c>
     </row>
     <row r="6">
@@ -612,22 +578,16 @@
         <v>0.9684</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8235</v>
+        <v>0.8245</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8245</v>
+        <v>0.9643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9643</v>
+        <v>0.9337</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8663</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="7">
@@ -643,22 +603,16 @@
         <v>0.9694</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8508</v>
+        <v>0.8516</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8516</v>
+        <v>0.9655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9655</v>
+        <v>0.9364</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8552999999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.9364</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.9602000000000001</v>
+        <v>0.9883</v>
       </c>
     </row>
     <row r="8">
@@ -674,22 +628,16 @@
         <v>0.9684</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8235</v>
+        <v>0.8245</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8245</v>
+        <v>0.9643</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9643</v>
+        <v>0.9337</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8663</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9878</v>
       </c>
     </row>
     <row r="9">
@@ -705,22 +653,16 @@
         <v>0.9681999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8232</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.9644</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9644</v>
+        <v>0.9332</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8483000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.9332</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9588</v>
+        <v>0.9876</v>
       </c>
     </row>
     <row r="10">
@@ -739,19 +681,13 @@
         <v>0.9204</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9204</v>
+        <v>0.95</v>
       </c>
       <c r="F10" t="n">
-        <v>0.95</v>
+        <v>0.9245</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="11">
@@ -770,19 +706,13 @@
         <v>0.9288</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9288</v>
+        <v>0.9527</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9527</v>
+        <v>0.9277</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8832</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.9277</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9635</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="12">
@@ -801,19 +731,13 @@
         <v>0.9204</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9204</v>
+        <v>0.95</v>
       </c>
       <c r="F12" t="n">
-        <v>0.95</v>
+        <v>0.9245</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.9245</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="13">
@@ -832,19 +756,13 @@
         <v>0.9199000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9502</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9502</v>
+        <v>0.9237</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8705000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.9237</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.9618</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="14">
@@ -863,19 +781,13 @@
         <v>0.8786</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8786</v>
+        <v>0.9163</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9163</v>
+        <v>0.9337</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8683999999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.9276</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="15">
@@ -894,19 +806,13 @@
         <v>0.8877</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8877</v>
+        <v>0.9208</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9208</v>
+        <v>0.9353</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8663999999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.9353</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.9306</v>
+        <v>0.9498</v>
       </c>
     </row>
     <row r="16">
@@ -925,19 +831,13 @@
         <v>0.8786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8786</v>
+        <v>0.9163</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9163</v>
+        <v>0.9337</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8683999999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.9337</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.9276</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="17">
@@ -956,19 +856,13 @@
         <v>0.8769</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8769</v>
+        <v>0.917</v>
       </c>
       <c r="F17" t="n">
-        <v>0.917</v>
+        <v>0.9331</v>
       </c>
       <c r="G17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.9331</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.9271</v>
+        <v>0.9483</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/TSTR_ML_Results_All_Metrics.xlsx
+++ b/dataset/TSTR_ML_Results_All_Metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,21 @@
           <t>T9_LHS</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>T10_AHAPSF1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>T11_AHAPSF2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>T12_AHAPSF3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -489,6 +504,15 @@
       <c r="G2" t="n">
         <v>0.9888</v>
       </c>
+      <c r="H2" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9755</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -514,6 +538,15 @@
       <c r="G3" t="n">
         <v>0.989</v>
       </c>
+      <c r="H3" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.9771</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9762</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -539,6 +572,15 @@
       <c r="G4" t="n">
         <v>0.9888</v>
       </c>
+      <c r="H4" t="n">
+        <v>0.9827</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9766</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9755</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -564,6 +606,15 @@
       <c r="G5" t="n">
         <v>0.9887</v>
       </c>
+      <c r="H5" t="n">
+        <v>0.9826</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9764</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9755</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -589,6 +640,15 @@
       <c r="G6" t="n">
         <v>0.9878</v>
       </c>
+      <c r="H6" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9681</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -614,6 +674,15 @@
       <c r="G7" t="n">
         <v>0.9883</v>
       </c>
+      <c r="H7" t="n">
+        <v>0.9825</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9520999999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -639,6 +708,15 @@
       <c r="G8" t="n">
         <v>0.9878</v>
       </c>
+      <c r="H8" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9681</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -664,6 +742,15 @@
       <c r="G9" t="n">
         <v>0.9876</v>
       </c>
+      <c r="H9" t="n">
+        <v>0.9816</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.968</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -689,6 +776,15 @@
       <c r="G10" t="n">
         <v>0.9673</v>
       </c>
+      <c r="H10" t="n">
+        <v>0.9612000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9202</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -714,6 +810,15 @@
       <c r="G11" t="n">
         <v>0.9687</v>
       </c>
+      <c r="H11" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.926</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -739,6 +844,15 @@
       <c r="G12" t="n">
         <v>0.9673</v>
       </c>
+      <c r="H12" t="n">
+        <v>0.9612000000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9202</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -764,6 +878,15 @@
       <c r="G13" t="n">
         <v>0.9673</v>
       </c>
+      <c r="H13" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9245</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9206</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -789,6 +912,15 @@
       <c r="G14" t="n">
         <v>0.949</v>
       </c>
+      <c r="H14" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9340000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -814,6 +946,15 @@
       <c r="G15" t="n">
         <v>0.9498</v>
       </c>
+      <c r="H15" t="n">
+        <v>0.9498</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.9353</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -839,6 +980,15 @@
       <c r="G16" t="n">
         <v>0.949</v>
       </c>
+      <c r="H16" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9340000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -863,6 +1013,15 @@
       </c>
       <c r="G17" t="n">
         <v>0.9483</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9308999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9340000000000001</v>
       </c>
     </row>
   </sheetData>
